--- a/models/9202_DCF_Model_20260906.xlsx
+++ b/models/9202_DCF_Model_20260906.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743997F0-E50E-441D-9C6F-E15A60914A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{187589AE-D6CE-4586-9B4B-76E9809B1F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -795,7 +795,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>Generated by pipeline on 2026-09-07 11:33, template rev a5a93a8</t>
+    <t>Generated by pipeline on 2026-09-07 13:17, template rev 1e927a2</t>
   </si>
   <si>
     <t>初期生成（手修正なし）</t>
@@ -1014,7 +1014,7 @@
     <t>generated_at</t>
   </si>
   <si>
-    <t>2026-09-07 11:33:44</t>
+    <t>2026-09-07 13:17:37</t>
   </si>
   <si>
     <t>guidance_note</t>
@@ -1083,7 +1083,7 @@
     <t>template_rev</t>
   </si>
   <si>
-    <t>a5a93a8</t>
+    <t>1e927a2</t>
   </si>
   <si>
     <t>ticker</t>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="C10" s="5">
         <f>IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0))</f>
-        <v>9398</v>
+        <v>6494</v>
       </c>
     </row>
     <row r="11" spans="2:5" ht="14" x14ac:dyDescent="0.3">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="C12" s="7">
         <f>IF(ISNUMBER(C10),(C10-C9)/C9,"N/A")</f>
-        <v>2.1331888648108017</v>
+        <v>1.1650275045840974</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="14" x14ac:dyDescent="0.3">
@@ -1764,11 +1764,11 @@
       </c>
       <c r="C17" s="11">
         <f>IF('DCF Model'!C62&lt;'DCF Model'!C16,"INVALID (EV &lt; net debt)",'DCF Model'!C64)</f>
-        <v>10595</v>
+        <v>4787</v>
       </c>
       <c r="D17" s="7">
         <f>IF(ISNUMBER(C17),(C17-C9)/C9,"N/A")</f>
-        <v>2.5322553758959825</v>
+        <v>0.59593265544257379</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="13.5" x14ac:dyDescent="0.25">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C21" s="6" t="str">
         <f>IF(COUNT(C16:C17)=0,"N/A",MIN(C16:C17)&amp;" - "&amp;MAX(C16:C17))</f>
-        <v>8201 - 10595</v>
+        <v>4787 - 8201</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="14" x14ac:dyDescent="0.3">
@@ -2533,7 +2533,7 @@
         <v>72</v>
       </c>
       <c r="C14" s="14">
-        <v>8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="C60" s="5">
         <f>C59*C14</f>
-        <v>5767224.1602291465</v>
+        <v>2234799.3620887944</v>
       </c>
     </row>
     <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="C61" s="5">
         <f>C60*G46</f>
-        <v>4102870.6185148116</v>
+        <v>1589862.3646744895</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="C62" s="5">
         <f>C58+C61</f>
-        <v>5006241.3907513078</v>
+        <v>2493233.1369109852</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="C63" s="5">
         <f>C62-C16</f>
-        <v>4584379.3907513078</v>
+        <v>2071371.1369109852</v>
       </c>
     </row>
     <row r="64" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="C64" s="24">
         <f>ROUND(C63*1000000/C15,0)</f>
-        <v>10595</v>
+        <v>4787</v>
       </c>
     </row>
     <row r="66" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="I3" s="14">
         <f>'DCF Model'!C14</f>
-        <v>8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="14" x14ac:dyDescent="0.3">
@@ -6178,31 +6178,31 @@
       </c>
       <c r="C17" s="42">
         <f>$I$3-3</f>
-        <v>5</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="D17" s="42">
         <f>$I$3-2</f>
-        <v>6</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E17" s="42">
         <f>$I$3-1</f>
-        <v>7</v>
+        <v>2.1</v>
       </c>
       <c r="F17" s="42">
         <f>$I$3</f>
-        <v>8</v>
+        <v>3.1</v>
       </c>
       <c r="G17" s="42">
         <f>$I$3+1</f>
-        <v>9</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="H17" s="42">
         <f>$I$3+2</f>
-        <v>10</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I17" s="42">
         <f>$I$3+3</f>
-        <v>11</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="18" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
@@ -6212,31 +6212,31 @@
       </c>
       <c r="C18" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B18)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B18)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B18)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B18)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B18)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*C$17/(1+$B18)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>7564</v>
+        <v>1332</v>
       </c>
       <c r="D18" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B18)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B18)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B18)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B18)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B18)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*D$17/(1+$B18)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8836</v>
+        <v>2603</v>
       </c>
       <c r="E18" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B18)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B18)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B18)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B18)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B18)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*E$17/(1+$B18)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>10108</v>
+        <v>3875</v>
       </c>
       <c r="F18" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B18)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B18)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B18)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B18)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B18)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*F$17/(1+$B18)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>11379</v>
+        <v>5147</v>
       </c>
       <c r="G18" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B18)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B18)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B18)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B18)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B18)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*G$17/(1+$B18)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>12651</v>
+        <v>6419</v>
       </c>
       <c r="H18" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B18)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B18)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B18)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B18)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B18)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*H$17/(1+$B18)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>13923</v>
+        <v>7691</v>
       </c>
       <c r="I18" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B18)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B18)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B18)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B18)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B18)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*I$17/(1+$B18)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>15195</v>
+        <v>8963</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
@@ -6246,31 +6246,31 @@
       </c>
       <c r="C19" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B19)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B19)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B19)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B19)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B19)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*C$17/(1+$B19)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>7384</v>
+        <v>1297</v>
       </c>
       <c r="D19" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B19)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B19)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B19)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B19)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B19)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*D$17/(1+$B19)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8626</v>
+        <v>2540</v>
       </c>
       <c r="E19" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B19)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B19)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B19)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B19)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B19)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*E$17/(1+$B19)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>9868</v>
+        <v>3782</v>
       </c>
       <c r="F19" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B19)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B19)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B19)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B19)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B19)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*F$17/(1+$B19)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>11111</v>
+        <v>5024</v>
       </c>
       <c r="G19" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B19)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B19)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B19)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B19)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B19)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*G$17/(1+$B19)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>12353</v>
+        <v>6266</v>
       </c>
       <c r="H19" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B19)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B19)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B19)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B19)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B19)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*H$17/(1+$B19)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>13595</v>
+        <v>7508</v>
       </c>
       <c r="I19" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B19)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B19)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B19)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B19)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B19)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*I$17/(1+$B19)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>14837</v>
+        <v>8751</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
@@ -6280,31 +6280,31 @@
       </c>
       <c r="C20" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B20)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B20)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B20)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B20)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B20)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*C$17/(1+$B20)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>7209</v>
+        <v>1264</v>
       </c>
       <c r="D20" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B20)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B20)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B20)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B20)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B20)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*D$17/(1+$B20)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8423</v>
+        <v>2477</v>
       </c>
       <c r="E20" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B20)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B20)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B20)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B20)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B20)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*E$17/(1+$B20)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>9636</v>
+        <v>3691</v>
       </c>
       <c r="F20" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B20)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B20)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B20)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B20)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B20)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*F$17/(1+$B20)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>10849</v>
+        <v>4904</v>
       </c>
       <c r="G20" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B20)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B20)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B20)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B20)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B20)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*G$17/(1+$B20)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>12062</v>
+        <v>6117</v>
       </c>
       <c r="H20" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B20)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B20)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B20)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B20)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B20)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*H$17/(1+$B20)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>13276</v>
+        <v>7331</v>
       </c>
       <c r="I20" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B20)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B20)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B20)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B20)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B20)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*I$17/(1+$B20)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>14489</v>
+        <v>8544</v>
       </c>
     </row>
     <row r="21" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
@@ -6314,31 +6314,31 @@
       </c>
       <c r="C21" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B21)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B21)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B21)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B21)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B21)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*C$17/(1+$B21)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>7039</v>
+        <v>1231</v>
       </c>
       <c r="D21" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B21)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B21)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B21)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B21)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B21)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*D$17/(1+$B21)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8224</v>
+        <v>2417</v>
       </c>
       <c r="E21" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B21)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B21)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B21)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B21)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B21)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*E$17/(1+$B21)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>9409</v>
+        <v>3602</v>
       </c>
       <c r="F21" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B21)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B21)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B21)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B21)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B21)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*F$17/(1+$B21)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>10595</v>
+        <v>4787</v>
       </c>
       <c r="G21" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B21)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B21)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B21)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B21)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B21)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*G$17/(1+$B21)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>11780</v>
+        <v>5972</v>
       </c>
       <c r="H21" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B21)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B21)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B21)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B21)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B21)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*H$17/(1+$B21)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>12965</v>
+        <v>7158</v>
       </c>
       <c r="I21" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B21)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B21)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B21)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B21)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B21)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*I$17/(1+$B21)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>14150</v>
+        <v>8343</v>
       </c>
     </row>
     <row r="22" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
@@ -6348,31 +6348,31 @@
       </c>
       <c r="C22" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B22)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B22)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B22)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B22)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B22)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*C$17/(1+$B22)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>6873</v>
+        <v>1199</v>
       </c>
       <c r="D22" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B22)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B22)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B22)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B22)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B22)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*D$17/(1+$B22)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8031</v>
+        <v>2357</v>
       </c>
       <c r="E22" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B22)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B22)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B22)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B22)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B22)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*E$17/(1+$B22)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>9189</v>
+        <v>3515</v>
       </c>
       <c r="F22" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B22)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B22)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B22)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B22)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B22)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*F$17/(1+$B22)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>10347</v>
+        <v>4673</v>
       </c>
       <c r="G22" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B22)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B22)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B22)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B22)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B22)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*G$17/(1+$B22)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>11505</v>
+        <v>5831</v>
       </c>
       <c r="H22" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B22)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B22)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B22)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B22)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B22)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*H$17/(1+$B22)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>12663</v>
+        <v>6989</v>
       </c>
       <c r="I22" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B22)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B22)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B22)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B22)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B22)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*I$17/(1+$B22)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>13821</v>
+        <v>8147</v>
       </c>
     </row>
     <row r="23" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
@@ -6382,31 +6382,31 @@
       </c>
       <c r="C23" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B23)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B23)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B23)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B23)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B23)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*C$17/(1+$B23)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>6712</v>
+        <v>1168</v>
       </c>
       <c r="D23" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B23)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B23)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B23)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B23)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B23)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*D$17/(1+$B23)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>7843</v>
+        <v>2300</v>
       </c>
       <c r="E23" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B23)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B23)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B23)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B23)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B23)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*E$17/(1+$B23)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8975</v>
+        <v>3431</v>
       </c>
       <c r="F23" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B23)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B23)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B23)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B23)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B23)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*F$17/(1+$B23)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>10106</v>
+        <v>4562</v>
       </c>
       <c r="G23" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B23)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B23)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B23)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B23)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B23)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*G$17/(1+$B23)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>11238</v>
+        <v>5694</v>
       </c>
       <c r="H23" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B23)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B23)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B23)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B23)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B23)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*H$17/(1+$B23)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>12369</v>
+        <v>6825</v>
       </c>
       <c r="I23" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B23)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B23)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B23)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B23)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B23)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*I$17/(1+$B23)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>13500</v>
+        <v>7957</v>
       </c>
     </row>
     <row r="24" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
@@ -6416,31 +6416,31 @@
       </c>
       <c r="C24" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B24)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B24)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B24)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B24)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B24)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*C$17/(1+$B24)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>6555</v>
+        <v>1138</v>
       </c>
       <c r="D24" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B24)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B24)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B24)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B24)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B24)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*D$17/(1+$B24)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>7661</v>
+        <v>2243</v>
       </c>
       <c r="E24" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B24)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B24)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B24)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B24)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B24)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*E$17/(1+$B24)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>8766</v>
+        <v>3349</v>
       </c>
       <c r="F24" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B24)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B24)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B24)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B24)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B24)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*F$17/(1+$B24)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>9872</v>
+        <v>4454</v>
       </c>
       <c r="G24" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B24)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B24)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B24)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B24)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B24)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*G$17/(1+$B24)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>10977</v>
+        <v>5560</v>
       </c>
       <c r="H24" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B24)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B24)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B24)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B24)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B24)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*H$17/(1+$B24)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>12083</v>
+        <v>6665</v>
       </c>
       <c r="I24" s="37">
         <f>IFERROR(ROUND(('DCF Model'!C45/(1+$B24)^('DCF Model'!C19+0)+'DCF Model'!D45/(1+$B24)^('DCF Model'!C19+1)+'DCF Model'!E45/(1+$B24)^('DCF Model'!C19+2)+'DCF Model'!F45/(1+$B24)^('DCF Model'!C19+3)+'DCF Model'!G45/(1+$B24)^('DCF Model'!C19+4)+('DCF Model'!G39+'DCF Model'!G42)*I$17/(1+$B24)^('DCF Model'!C19+4)-'DCF Model'!C16)*1000000/'DCF Model'!C15,0),"")</f>
-        <v>13188</v>
+        <v>7771</v>
       </c>
     </row>
     <row r="26" spans="2:9" ht="14" x14ac:dyDescent="0.3">
